--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90298</v>
+        <v>90301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90301</v>
+        <v>90304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90304</v>
+        <v>90308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90308</v>
+        <v>90315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90315</v>
+        <v>90317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90317</v>
+        <v>90318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92848</v>
+        <v>92851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90321</v>
+        <v>90323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92853</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90323</v>
+        <v>90327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90327</v>
+        <v>90328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90328</v>
+        <v>90331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129135678</v>
       </c>
       <c r="B2" t="n">
-        <v>92861</v>
+        <v>92889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129135617</v>
       </c>
       <c r="B3" t="n">
-        <v>90331</v>
+        <v>90359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49131-2025 artfynd.xlsx
+++ b/artfynd/A 49131-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129135678</v>
+        <v>129135617</v>
       </c>
       <c r="B2" t="n">
-        <v>92889</v>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogstorp, Upl</t>
+          <t>skogstorp, Adelsö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642040</v>
+        <v>642027</v>
       </c>
       <c r="R2" t="n">
-        <v>6581782</v>
+        <v>6581744</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129135617</v>
+        <v>129135678</v>
       </c>
       <c r="B3" t="n">
-        <v>90359</v>
+        <v>93223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1596</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,17 +820,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>skogstorp, Adelsö, Upl</t>
+          <t>Skogstorp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642027</v>
+        <v>642040</v>
       </c>
       <c r="R3" t="n">
-        <v>6581744</v>
+        <v>6581782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,6 +894,116 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129074500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogstorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>642061</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6581755</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Adelsö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
